--- a/submission_summary.xlsx
+++ b/submission_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,7 +697,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Excruciating Musical Suicide Bombing</t>
+          <t>Swaying With Lighter Held Aloft</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Excruciating Musical Suicide Bombing</t>
+          <t>Swaying With Lighter Held Aloft</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Excruciating Musical Suicide Bombing</t>
+          <t>Swaying With Lighter Held Aloft</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>II. Andantino</t>
+          <t>Keyboard Concerto in G Major, Wq. 44: II. Andantino</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Excruciating Musical Suicide Bombing</t>
+          <t>Swaying With Lighter Held Aloft</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Excruciating Musical Suicide Bombing</t>
+          <t>Swaying With Lighter Held Aloft</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3586,6 +3586,3108 @@
       </c>
       <c r="G96" t="n">
         <v>32</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Killing Joke</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Change - 2005 Digital Remaster</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>The Notwist</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pick up the Phone</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>The Fauves</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Get In Line</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Anjali</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Turn It On</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Hunters &amp; Collectors</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Throw Your Arms Around Me</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Swaying With Lighter Held Aloft</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Pale Lights</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Jean, Bring the Flowers</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>GusGus</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Add This Song</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>The Orielles</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Let Your Dog Tooth Grow</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Dua Lipa</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Don't Start Now</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IAMX</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Spit It Out</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Pigs Pigs Pigs Pigs Pigs Pigs Pigs</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pipe Down!</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Neko Case</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Twist the Knife</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Diamanda Galás</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Let My People Go</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Pylon</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Feast On My Heart - Remastered</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>The Cat</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Do the Watusi</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Nitzer Ebb</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Join in the Chant</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Chemtrails</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Join Our Death Cult</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Agnes Obel</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Stretch Your Eyes</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Old 97's</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Dance with Me</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Leave Her Alone</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>The Lord Weird Slough Feg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>We'll Meet Again</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>7</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>The Kills</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Future Starts Slow</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Idlewild</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>A Film for the Future</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>7</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Pedro The Lion</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>When They Realy Get To Know You They Will Run</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>7</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Whyte Horses</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Next Year Will Be Mine</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>7</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Andy Prieboy</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Tomorrow Wendy</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>7</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Quincy Jones, Tevin Campbell</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Tomorrow (A Better You, Better Me)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>7</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Soko</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>We Might Be Dead by Tomorrow</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>7</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>The Pains Of Being Pure At Heart</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Come Saturday</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Shoes</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Tomorrow Night</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Swaying With Lighter Held Aloft</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>7</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Patrick Wolf</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>The Future</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>7</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sparks</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>In The Future</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>7</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>The Church</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Memories In Future Tense - 2002 Digital Remaster</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>7</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Alvvays</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Dreams Tonite</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>7</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>One Day</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>7</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Love Shop</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>En Nat Bliver Det Sommer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>7</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Tame Impala</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Apocalypse Dreams</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>7</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Elo</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Tommorow</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>7</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Big Red Machine, Anaïs Mitchell</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Latter Days</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>7</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Tomorrow</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Édouard Tremblay-Grenier</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Je rêve</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>8</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Fiddlehead</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Sleepyhead</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>8</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Bongwater</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>His Old Look</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>8</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Great Lake Swimmers</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>She Comes To Me In Dreams</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>8</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>This Heat</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>8</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Thee Oh Sees</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>The Dream</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>8</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Belle and Sebastian</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Judy and the Dream of Horses</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>8</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Kronos Quartet, Laurie Anderson</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Dreams</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>8</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Mercyful Fate</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Nightmare</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Arthur Russell</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Iowa Dream</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>8</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Stars</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Asleep</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>8</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>H₂O</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Dream to Sleep</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>8</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Queensrÿche</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Silent Lucidity - Remastered 2003</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Swaying With Lighter Held Aloft</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>8</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Memoryhouse</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Sleep Patterns</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>8</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>The Romantics</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Talking In Your Sleep (2023 Remaster)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>8</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Hans Zimmer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Dream Within a Dream</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>8</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>The Smiths</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Asleep - 2011 Remaster</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>8</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>The Kinks</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>I Go to Sleep - Demo Version</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Allman Brothers Band</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Dreams</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>8</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>John Waite</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>9</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Aimee Mann</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Save Me</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>9</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>New Order</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Shellshock - 7" Edit; 2015 Remaster</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>9</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Kavinsky</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Nightcall</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>9</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>The Dream Academy</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>The Edge of Forever</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>9</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>John C. Williams</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Cavatina (Theme from "The Deer Hunter") - 2010 Remastered Version</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>9</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Perfume Genius</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Queen</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>9</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Paul Giovanni, Magnet</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Willow's Song</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>9</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Rebekah Del Rio</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Crying - From 'Mulholland Drive'</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Lee Potter</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>9</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Yusuf / Cat Stevens</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Trouble</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>9</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Flash and the Pan</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Waiting for a Train</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>9</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Boards of Canada</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>The Word Becomes Flesh</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>9</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Nine Below Zero</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Eleven Plus Eleven</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>9</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Philip Glass</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pruit Igoe</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>9</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Colin Hay</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Overkill - Acoustic Version</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>9</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Buffalo Tom</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Late At Night</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>9</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>John C. Reilly</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Beautiful Ride</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Swaying With Lighter Held Aloft</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>9</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Daniel White</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Belle (Extrait de la série TV "Belle et Sébastien", 1965)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>9</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Cinder Well</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>The Wise Man's Song (Original Theme from Small Prophets)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>9</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Hollywood 4-5-92</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Ibliss</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>High Life</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mike Sproge</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>10</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Soap&amp;Skin</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Me and the Devil</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>10</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Sea Power</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>No Lucifer</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Neil Jones</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>10</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Backworld</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>The Devil's Plaything</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Sparkle Motion</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>10</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Zeal &amp; Ardor</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Devil Is Fine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Lasse Grosbøl</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>10</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Andy Shauf</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Satan</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Nadeem</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>10</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Twin Temple</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Satan's a Woman</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Rocket From The Chris</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>10</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PJ Harvey</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>The Devil</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ben Campbell</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>10</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Butthole Surfers</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Dust Devil</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>transmission11k</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>10</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Murder By Death</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>The Devil in Mexico</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>David Z</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>10</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Satan's Pilgrims</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Shit Sandwich</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Caroline Rouwalk</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>10</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Mt. Mountain</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Diablo</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Swaying With Lighter Held Aloft</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>10</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Paul Jacobs</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Dancing With the Devil</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>zaxxon25</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>10</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Spare Snare</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Hit Me, Satan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Girvan Burnside</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>10</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Worriedaboutsatan</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>A Lost History</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tony Heywood</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>10</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Miike Snow</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Devil's Work</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BusterMumbles</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>10</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Marnie Stern</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>The Devil's In the Details</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Alister Shew</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>10</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>the bird and the bee</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Runnin’ with the Devil</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Michael O'Hara</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Firefly 8</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>10</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Friend of the Devil</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
